--- a/forms/trg/Formulir_TRG_bite-fish.xlsx
+++ b/forms/trg/Formulir_TRG_bite-fish.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B23)</f>
+        <f>COUNTA(Anggota!B5:B24)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F23)</f>
+        <f>COUNTA(Anggota!F5:F24)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,12 +913,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Abdul Haris, M.Si</t>
+          <t>Prof. Andi Iqbal Burhanuddin, M.Fish.Science., Ph.D</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -928,22 +928,18 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Marine Biology</t>
+          <t>Fish Taxonomy</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-7535-4514</t>
-        </is>
-      </c>
+      <c r="J5" s="12" t="n"/>
       <c r="K5" s="12" t="n"/>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>56581763400</t>
+          <t>57215376841</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -958,12 +954,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. Budimawan, DEA, Ph.D</t>
+          <t>Prof. Dr. Abdul Haris, M.Si</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -973,7 +969,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Fisheries Biology</t>
+          <t>Marine Biology</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -982,13 +978,13 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-0566-2305</t>
+          <t>0000-0001-7535-4514</t>
         </is>
       </c>
       <c r="K6" s="12" t="n"/>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>7409768808</t>
+          <t>56581763400</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1003,12 +999,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Andi Annisar Dzati Iffah, M.Si</t>
+          <t>Prof. Budimawan, DEA, Ph.D</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1018,16 +1014,24 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Fish Taxonomy</t>
+          <t>Fisheries Biology</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="12" t="n"/>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-0566-2305</t>
+        </is>
+      </c>
       <c r="K7" s="12" t="n"/>
-      <c r="L7" s="12" t="n"/>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>7409768808</t>
+        </is>
+      </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1040,17 +1044,17 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Prof Hiroyuki Motomura, Ph.D</t>
+          <t>Andi Annisar Dzati Iffah, M.Si</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Kagoshima University Museum</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -1062,17 +1066,9 @@
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-7448-2482</t>
-        </is>
-      </c>
+      <c r="J8" s="12" t="n"/>
       <c r="K8" s="12" t="n"/>
-      <c r="L8" s="11" t="inlineStr">
-        <is>
-          <t>56259741300</t>
-        </is>
-      </c>
+      <c r="L8" s="12" t="n"/>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1085,17 +1081,17 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Dr. Nurjirana, S.Kel., M.Si</t>
+          <t>Prof Hiroyuki Motomura, Ph.D</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>National Research and Innovation Agency</t>
+          <t>Kagoshima University Museum</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -1109,13 +1105,13 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-4801-1481</t>
+          <t>0000-0002-7448-2482</t>
         </is>
       </c>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>57205482702</t>
+          <t>56259741300</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1130,17 +1126,17 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Ardyansyah Kahar, S.Kel</t>
+          <t>Dr. Nurjirana, S.Kel., M.Si</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>National Research and Innovation Agency</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -1152,9 +1148,17 @@
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
-      <c r="J10" s="12" t="n"/>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-4801-1481</t>
+        </is>
+      </c>
       <c r="K10" s="12" t="n"/>
-      <c r="L10" s="12" t="n"/>
+      <c r="L10" s="11" t="inlineStr">
+        <is>
+          <t>57205482702</t>
+        </is>
+      </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1167,22 +1171,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>A. Muhammad Raihan Shafwan</t>
+          <t>Ardyansyah Kahar, S.Kel</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
           <t>Fish Taxonomy</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>ENFISH Team</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1202,10 +1206,26 @@
       <c r="A12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="11" t="n"/>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>A. Muhammad Raihan Shafwan</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Fish Taxonomy</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>ENFISH Team</t>
+        </is>
+      </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
@@ -1213,7 +1233,11 @@
       <c r="J12" s="12" t="n"/>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="12" t="n"/>
-      <c r="M12" s="12" t="n"/>
+      <c r="M12" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1402,15 +1426,32 @@
       <c r="L23" s="12" t="n"/>
       <c r="M23" s="12" t="n"/>
     </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="12" t="n"/>
+      <c r="G24" s="12" t="n"/>
+      <c r="H24" s="12" t="n"/>
+      <c r="I24" s="12" t="n"/>
+      <c r="J24" s="12" t="n"/>
+      <c r="K24" s="12" t="n"/>
+      <c r="L24" s="12" t="n"/>
+      <c r="M24" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
